--- a/data-source/banchan-50.xlsx
+++ b/data-source/banchan-50.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\K-BanChan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\K-BanChan\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2EC4833-2ACD-4A30-A572-DE34DB2F57CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590DCF96-C8ED-47E4-BEAF-C4F9A3763D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="329">
   <si>
     <t>순위</t>
   </si>
@@ -1000,13 +1000,53 @@
   </si>
   <si>
     <t>X (소고기 포함)</t>
+  </si>
+  <si>
+    <t>조리법응용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>재료 구입</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>∙</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>준비 가이드</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비건 여부</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>반찬 스토리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1029,6 +1069,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1038,7 +1086,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1061,13 +1109,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3824,7 +3886,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="16.796875" customWidth="1"/>
@@ -3834,7 +3896,7 @@
     <col min="8" max="8" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3851,16 +3913,19 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>325</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>328</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+        <v>327</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3886,7 +3951,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>16</v>
       </c>
@@ -3912,7 +3977,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>17</v>
       </c>
@@ -3938,7 +4003,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>25</v>
       </c>
@@ -3964,7 +4029,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>27</v>
       </c>
@@ -3990,7 +4055,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>32</v>
       </c>
@@ -4016,7 +4081,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>33</v>
       </c>
@@ -4042,7 +4107,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>34</v>
       </c>
@@ -4068,7 +4133,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>40</v>
       </c>
@@ -4094,7 +4159,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>43</v>
       </c>
@@ -4120,7 +4185,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>44</v>
       </c>
@@ -4146,7 +4211,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>45</v>
       </c>
@@ -4172,7 +4237,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>47</v>
       </c>

--- a/data-source/banchan-50.xlsx
+++ b/data-source/banchan-50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\K-BanChan\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{590DCF96-C8ED-47E4-BEAF-C4F9A3763D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6AC62C-4B34-4299-9AB2-EE74929BC332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="328">
   <si>
     <t>순위</t>
   </si>
@@ -42,15 +42,6 @@
     <t>조리법</t>
   </si>
   <si>
-    <t>팁</t>
-  </si>
-  <si>
-    <t>블로그/기사 주요 요약(G)</t>
-  </si>
-  <si>
-    <t>비건 여부(H)</t>
-  </si>
-  <si>
     <t>계란말이</t>
   </si>
   <si>
@@ -1000,10 +991,6 @@
   </si>
   <si>
     <t>X (소고기 포함)</t>
-  </si>
-  <si>
-    <t>조리법응용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1039,6 +1026,18 @@
   </si>
   <si>
     <t>반찬 스토리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매운맛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조리법 응용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>재료 구입∙준비 가이드</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1086,7 +1085,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1120,16 +1119,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1436,13 +1450,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="7" max="7" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="11.8984375" customWidth="1"/>
+    <col min="3" max="3" width="12.296875" customWidth="1"/>
+    <col min="4" max="5" width="13.796875" customWidth="1"/>
+    <col min="6" max="6" width="14.8984375" customWidth="1"/>
+    <col min="7" max="7" width="24.69921875" customWidth="1"/>
+    <col min="8" max="8" width="18.59765625" customWidth="1"/>
+    <col min="9" max="10" width="18.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1459,403 +1479,409 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>326</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>324</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+        <v>323</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H8" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H9" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H10" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H11" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F12" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H12" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F13" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G13" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H13" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F14" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G14" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H14" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F15" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H15" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F16" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G16" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H16" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
@@ -1863,25 +1889,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F17" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G17" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H17" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
@@ -1889,25 +1915,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F18" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G18" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H18" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -1915,25 +1941,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F19" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G19" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H19" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
@@ -1941,25 +1967,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E20" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F20" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G20" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H20" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
@@ -1967,25 +1993,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F21" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G21" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H21" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
@@ -1993,25 +2019,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E22" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F22" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G22" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H22" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
@@ -2019,25 +2045,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E23" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F23" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G23" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H23" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -2045,25 +2071,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F24" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G24" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H24" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
@@ -2071,25 +2097,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E25" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F25" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G25" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H25" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
@@ -2097,25 +2123,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E26" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F26" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G26" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H26" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
@@ -2123,25 +2149,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E27" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F27" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G27" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H27" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
@@ -2149,25 +2175,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F28" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G28" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H28" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
@@ -2175,25 +2201,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F29" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G29" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H29" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
@@ -2201,25 +2227,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E30" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F30" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G30" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H30" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
@@ -2227,25 +2253,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E31" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F31" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G31" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H31" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.4">
@@ -2253,25 +2279,25 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E32" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F32" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G32" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H32" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
@@ -2279,25 +2305,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E33" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F33" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G33" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H33" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
@@ -2305,25 +2331,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E34" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F34" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G34" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H34" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
@@ -2331,25 +2357,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E35" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F35" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G35" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H35" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
@@ -2357,25 +2383,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E36" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F36" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G36" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H36" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
@@ -2383,25 +2409,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E37" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F37" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G37" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H37" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
@@ -2409,25 +2435,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E38" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F38" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G38" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H38" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
@@ -2435,25 +2461,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D39" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E39" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F39" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G39" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H39" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
@@ -2461,25 +2487,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E40" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F40" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G40" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="H40" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.4">
@@ -2487,25 +2513,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E41" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F41" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G41" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H41" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
@@ -2513,25 +2539,25 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D42" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F42" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G42" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H42" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.4">
@@ -2539,25 +2565,25 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F43" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G43" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H43" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
@@ -2565,25 +2591,25 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E44" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F44" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G44" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H44" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.4">
@@ -2591,25 +2617,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D45" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E45" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F45" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G45" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H45" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.4">
@@ -2617,25 +2643,25 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E46" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F46" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G46" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H46" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.4">
@@ -2643,25 +2669,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D47" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E47" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F47" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G47" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H47" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
@@ -2669,25 +2695,25 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C48" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E48" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F48" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G48" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H48" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
@@ -2695,25 +2721,25 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D49" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E49" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F49" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G49" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H49" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.4">
@@ -2721,25 +2747,25 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E50" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F50" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G50" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
@@ -2747,25 +2773,25 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D51" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E51" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F51" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G51" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H51" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -2776,10 +2802,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="7" max="9" width="33.69921875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2796,351 +2825,357 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>326</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>324</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+        <v>323</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H8" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H9" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H10" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H11" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G12" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H12" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F13" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G13" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H13" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F14" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G14" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H14" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -3151,10 +3186,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="6" max="6" width="18.3984375" customWidth="1"/>
+    <col min="7" max="7" width="23.19921875" customWidth="1"/>
+    <col min="8" max="9" width="20.59765625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3171,169 +3211,175 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>326</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>324</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+        <v>323</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H4" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3344,10 +3390,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="6" max="6" width="15.3984375" customWidth="1"/>
+    <col min="7" max="7" width="15.59765625" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="23.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3364,377 +3416,383 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>326</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>324</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+        <v>323</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G8" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H8" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G9" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H9" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="G10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H10" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E11" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F11" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G11" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="H11" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F12" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G12" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H12" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E13" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F13" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G13" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H13" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F14" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G14" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H14" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F15" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G15" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H15" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3745,10 +3803,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="6" max="6" width="20.19921875" customWidth="1"/>
+    <col min="7" max="7" width="24.5" customWidth="1"/>
+    <col min="8" max="8" width="15.8984375" customWidth="1"/>
+    <col min="9" max="9" width="19.296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3765,117 +3829,123 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>326</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>324</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+        <v>323</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>19</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3886,17 +3956,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="16.796875" customWidth="1"/>
     <col min="3" max="3" width="16.8984375" customWidth="1"/>
     <col min="4" max="4" width="15.796875" customWidth="1"/>
+    <col min="5" max="5" width="12.3984375" customWidth="1"/>
+    <col min="6" max="6" width="19.796875" customWidth="1"/>
     <col min="7" max="7" width="14.19921875" customWidth="1"/>
     <col min="8" max="8" width="20.5" customWidth="1"/>
+    <col min="9" max="10" width="24.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3913,354 +3986,396 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+        <v>305</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+        <v>314</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="H5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+        <v>314</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+        <v>317</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H8" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+        <v>312</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H9" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+        <v>305</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F10" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="G10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H10" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H11" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+        <v>321</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E12" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F12" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G12" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H12" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F13" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G13" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H13" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+        <v>307</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E14" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F14" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H14" t="s">
-        <v>310</v>
+        <v>307</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/banchan-50.xlsx
+++ b/data-source/banchan-50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\K-BanChan\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6AC62C-4B34-4299-9AB2-EE74929BC332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE2397A-492A-4359-96A1-66150273ABE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,13 +19,14 @@
     <sheet name="무침" sheetId="4" r:id="rId4"/>
     <sheet name="나물" sheetId="5" r:id="rId5"/>
     <sheet name="기타(장아찌_전_찜)" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="331">
   <si>
     <t>순위</t>
   </si>
@@ -1038,6 +1039,18 @@
   </si>
   <si>
     <t>재료 구입∙준비 가이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조리법 분류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사진 파일명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사진파일명</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1132,12 +1145,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1450,7 +1466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="11.8984375" customWidth="1"/>
@@ -1459,10 +1475,12 @@
     <col min="6" max="6" width="14.8984375" customWidth="1"/>
     <col min="7" max="7" width="24.69921875" customWidth="1"/>
     <col min="8" max="8" width="18.59765625" customWidth="1"/>
-    <col min="9" max="10" width="18.796875" customWidth="1"/>
+    <col min="9" max="9" width="18.796875" customWidth="1"/>
+    <col min="10" max="10" width="10.3984375" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1487,14 +1505,20 @@
       <c r="H1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K1" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1520,7 +1544,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1546,7 +1570,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1572,7 +1596,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1598,7 +1622,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1624,7 +1648,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1650,7 +1674,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1676,7 +1700,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1702,7 +1726,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1728,7 +1752,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1754,7 +1778,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1780,7 +1804,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1806,7 +1830,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1832,7 +1856,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1858,7 +1882,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2802,13 +2826,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="7" max="9" width="33.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2833,14 +2857,20 @@
       <c r="H1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K1" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>2</v>
       </c>
@@ -2865,8 +2895,11 @@
       <c r="H2" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>8</v>
       </c>
@@ -2891,8 +2924,11 @@
       <c r="H3" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>9</v>
       </c>
@@ -2917,8 +2953,11 @@
       <c r="H4" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>11</v>
       </c>
@@ -2943,8 +2982,11 @@
       <c r="H5" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>13</v>
       </c>
@@ -2969,8 +3011,11 @@
       <c r="H6" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>15</v>
       </c>
@@ -2995,8 +3040,11 @@
       <c r="H7" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>18</v>
       </c>
@@ -3021,8 +3069,11 @@
       <c r="H8" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>22</v>
       </c>
@@ -3047,8 +3098,11 @@
       <c r="H9" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>23</v>
       </c>
@@ -3073,8 +3127,11 @@
       <c r="H10" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>29</v>
       </c>
@@ -3099,8 +3156,11 @@
       <c r="H11" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>30</v>
       </c>
@@ -3125,8 +3185,11 @@
       <c r="H12" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>31</v>
       </c>
@@ -3151,8 +3214,11 @@
       <c r="H13" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>42</v>
       </c>
@@ -3176,6 +3242,9 @@
       </c>
       <c r="H14" t="s">
         <v>320</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3186,7 +3255,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="6" max="6" width="18.3984375" customWidth="1"/>
@@ -3194,7 +3263,7 @@
     <col min="8" max="9" width="20.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3219,14 +3288,20 @@
       <c r="H1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K1" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>3</v>
       </c>
@@ -3251,8 +3326,11 @@
       <c r="H2" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>5</v>
       </c>
@@ -3277,8 +3355,11 @@
       <c r="H3" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>14</v>
       </c>
@@ -3303,8 +3384,11 @@
       <c r="H4" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>21</v>
       </c>
@@ -3329,8 +3413,11 @@
       <c r="H5" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>36</v>
       </c>
@@ -3355,8 +3442,11 @@
       <c r="H6" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>37</v>
       </c>
@@ -3380,6 +3470,9 @@
       </c>
       <c r="H7" t="s">
         <v>307</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3390,7 +3483,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="6" max="6" width="15.3984375" customWidth="1"/>
@@ -3399,7 +3492,7 @@
     <col min="9" max="9" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3424,14 +3517,20 @@
       <c r="H1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K1" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>4</v>
       </c>
@@ -3456,8 +3555,11 @@
       <c r="H2" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>6</v>
       </c>
@@ -3482,8 +3584,11 @@
       <c r="H3" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>10</v>
       </c>
@@ -3508,8 +3613,11 @@
       <c r="H4" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>20</v>
       </c>
@@ -3534,8 +3642,11 @@
       <c r="H5" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>24</v>
       </c>
@@ -3560,8 +3671,11 @@
       <c r="H6" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>26</v>
       </c>
@@ -3586,8 +3700,11 @@
       <c r="H7" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>28</v>
       </c>
@@ -3612,8 +3729,11 @@
       <c r="H8" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>35</v>
       </c>
@@ -3638,8 +3758,11 @@
       <c r="H9" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>38</v>
       </c>
@@ -3664,8 +3787,11 @@
       <c r="H10" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>39</v>
       </c>
@@ -3690,8 +3816,11 @@
       <c r="H11" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>41</v>
       </c>
@@ -3716,8 +3845,11 @@
       <c r="H12" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>46</v>
       </c>
@@ -3742,8 +3874,11 @@
       <c r="H13" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>48</v>
       </c>
@@ -3768,8 +3903,11 @@
       <c r="H14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>49</v>
       </c>
@@ -3793,6 +3931,9 @@
       </c>
       <c r="H15" t="s">
         <v>307</v>
+      </c>
+      <c r="K15">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3803,7 +3944,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="6" max="6" width="20.19921875" customWidth="1"/>
@@ -3812,7 +3953,7 @@
     <col min="9" max="9" width="19.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3837,14 +3978,20 @@
       <c r="H1" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K1" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>7</v>
       </c>
@@ -3869,8 +4016,14 @@
       <c r="H2" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>12</v>
       </c>
@@ -3895,8 +4048,14 @@
       <c r="H3" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>19</v>
       </c>
@@ -3921,8 +4080,14 @@
       <c r="H4" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>50</v>
       </c>
@@ -3946,6 +4111,12 @@
       </c>
       <c r="H5" t="s">
         <v>307</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3956,7 +4127,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="16.796875" customWidth="1"/>
@@ -3965,11 +4136,14 @@
     <col min="5" max="5" width="12.3984375" customWidth="1"/>
     <col min="6" max="6" width="19.796875" customWidth="1"/>
     <col min="7" max="7" width="14.19921875" customWidth="1"/>
-    <col min="8" max="8" width="20.5" customWidth="1"/>
-    <col min="9" max="10" width="24.796875" customWidth="1"/>
+    <col min="8" max="8" width="15.796875" customWidth="1"/>
+    <col min="9" max="9" width="24.796875" customWidth="1"/>
+    <col min="10" max="10" width="9.296875" customWidth="1"/>
+    <col min="11" max="11" width="12.09765625" customWidth="1"/>
+    <col min="12" max="12" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3997,11 +4171,17 @@
       <c r="I1" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="K1" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4030,7 +4210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>16</v>
       </c>
@@ -4059,7 +4239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>17</v>
       </c>
@@ -4088,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>25</v>
       </c>
@@ -4117,7 +4297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>27</v>
       </c>
@@ -4146,7 +4326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>32</v>
       </c>
@@ -4175,7 +4355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>33</v>
       </c>
@@ -4204,7 +4384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>34</v>
       </c>
@@ -4233,7 +4413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>40</v>
       </c>
@@ -4262,7 +4442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>43</v>
       </c>
@@ -4291,7 +4471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>44</v>
       </c>
@@ -4320,7 +4500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>45</v>
       </c>
@@ -4349,7 +4529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>47</v>
       </c>
@@ -4382,4 +4562,15 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEA7B12-CD66-4456-B8BA-D07DD0235DD7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data-source/banchan-50.xlsx
+++ b/data-source/banchan-50.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\K-BanChan\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE2397A-492A-4359-96A1-66150273ABE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF9A785-D117-40E6-9C90-7D43CF8B4AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="전체_종합요약" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="334">
   <si>
     <t>순위</t>
   </si>
@@ -1051,6 +1051,18 @@
   </si>
   <si>
     <t>사진파일명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠팡 링크</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아마존 링크</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라쿠텐 링크</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1145,7 +1157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1157,9 +1169,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1466,7 +1475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="11.8984375" customWidth="1"/>
@@ -1480,7 +1489,7 @@
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1511,14 +1520,23 @@
       <c r="J1" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M1" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1544,7 +1562,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1570,7 +1588,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1596,7 +1614,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1622,7 +1640,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1648,7 +1666,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1674,7 +1692,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1700,7 +1718,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1726,7 +1744,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1752,7 +1770,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1778,7 +1796,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1804,7 +1822,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1830,7 +1848,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1856,7 +1874,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1882,7 +1900,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2863,10 +2881,10 @@
       <c r="J1" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>330</v>
       </c>
     </row>
@@ -3294,10 +3312,10 @@
       <c r="J1" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="3" t="s">
         <v>329</v>
       </c>
     </row>
@@ -3523,10 +3541,10 @@
       <c r="J1" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>329</v>
       </c>
     </row>
@@ -3984,10 +4002,10 @@
       <c r="J1" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>329</v>
       </c>
     </row>
@@ -4174,10 +4192,10 @@
       <c r="J1" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>329</v>
       </c>
     </row>

--- a/data-source/banchan-50.xlsx
+++ b/data-source/banchan-50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\K-BanChan\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF9A785-D117-40E6-9C90-7D43CF8B4AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02736BD3-33B2-4D12-A25B-8D2350D6EBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,7 @@
     <sheet name="Sheet1" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -1157,7 +1158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1166,9 +1167,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1480,7 +1478,8 @@
   <cols>
     <col min="2" max="2" width="11.8984375" customWidth="1"/>
     <col min="3" max="3" width="12.296875" customWidth="1"/>
-    <col min="4" max="5" width="13.796875" customWidth="1"/>
+    <col min="4" max="4" width="44.296875" customWidth="1"/>
+    <col min="5" max="5" width="13.796875" customWidth="1"/>
     <col min="6" max="6" width="14.8984375" customWidth="1"/>
     <col min="7" max="7" width="24.69921875" customWidth="1"/>
     <col min="8" max="8" width="18.59765625" customWidth="1"/>
@@ -1526,13 +1525,13 @@
       <c r="L1" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="2" t="s">
         <v>333</v>
       </c>
     </row>
@@ -1926,7 +1925,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
